--- a/input_data/admin_data/SLV/_clean/wages-SLV.xlsx
+++ b/input_data/admin_data/SLV/_clean/wages-SLV.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="8">
   <si>
     <t>year</t>
   </si>

--- a/input_data/admin_data/SLV/_clean/wages-SLV.xlsx
+++ b/input_data/admin_data/SLV/_clean/wages-SLV.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1245" uniqueCount="8">
   <si>
     <t>year</t>
   </si>

--- a/input_data/admin_data/SLV/_clean/wages-SLV.xlsx
+++ b/input_data/admin_data/SLV/_clean/wages-SLV.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1245" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1743" uniqueCount="8">
   <si>
     <t>year</t>
   </si>

--- a/input_data/admin_data/SLV/_clean/wages-SLV.xlsx
+++ b/input_data/admin_data/SLV/_clean/wages-SLV.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1743" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2241" uniqueCount="8">
   <si>
     <t>year</t>
   </si>
